--- a/templates/mau_doisoat_ctv.xlsx
+++ b/templates/mau_doisoat_ctv.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\namnh4\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\programme\git_repository\bmk\bmk-ctv-service\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6375E85-9E29-46ED-AA15-776DE4C467C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E5C3370-3FAC-473E-A144-F329DD865CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HROS30.06" sheetId="1" r:id="rId1"/>
@@ -186,7 +186,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -211,6 +211,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -554,7 +560,7 @@
     <col min="2" max="2" width="15.1796875" style="3" customWidth="1"/>
     <col min="3" max="3" width="22.7265625" customWidth="1"/>
     <col min="4" max="5" width="22.453125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="9.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.26953125" style="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.7265625" style="3" customWidth="1"/>
     <col min="8" max="8" width="5.26953125" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.453125" style="3" customWidth="1"/>
@@ -620,7 +626,7 @@
       <c r="E4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="11" t="s">
         <v>12</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -646,7 +652,6 @@
       <c r="B5" s="2"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
@@ -658,7 +663,6 @@
       <c r="B6" s="2"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
@@ -670,7 +674,6 @@
       <c r="B7" s="2"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
@@ -682,7 +685,6 @@
       <c r="B8" s="2"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
@@ -694,7 +696,6 @@
       <c r="B9" s="2"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -706,7 +707,6 @@
       <c r="B10" s="2"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
@@ -718,7 +718,6 @@
       <c r="B11" s="2"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
@@ -730,7 +729,6 @@
       <c r="B12" s="2"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -742,7 +740,6 @@
       <c r="B13" s="2"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
@@ -754,7 +751,6 @@
       <c r="B14" s="2"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
@@ -765,7 +761,6 @@
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
@@ -776,7 +771,6 @@
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
@@ -787,7 +781,6 @@
     <row r="17" spans="4:12" x14ac:dyDescent="0.35">
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
@@ -798,7 +791,6 @@
     <row r="18" spans="4:12" x14ac:dyDescent="0.35">
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
@@ -809,7 +801,6 @@
     <row r="19" spans="4:12" x14ac:dyDescent="0.35">
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
@@ -820,7 +811,6 @@
     <row r="20" spans="4:12" x14ac:dyDescent="0.35">
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
@@ -831,7 +821,6 @@
     <row r="21" spans="4:12" x14ac:dyDescent="0.35">
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
@@ -842,7 +831,6 @@
     <row r="22" spans="4:12" x14ac:dyDescent="0.35">
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
@@ -853,7 +841,6 @@
     <row r="23" spans="4:12" x14ac:dyDescent="0.35">
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
@@ -864,7 +851,6 @@
     <row r="24" spans="4:12" x14ac:dyDescent="0.35">
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
@@ -875,7 +861,6 @@
     <row r="25" spans="4:12" x14ac:dyDescent="0.35">
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
@@ -886,7 +871,6 @@
     <row r="26" spans="4:12" x14ac:dyDescent="0.35">
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
@@ -897,7 +881,6 @@
     <row r="27" spans="4:12" x14ac:dyDescent="0.35">
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
@@ -908,7 +891,6 @@
     <row r="28" spans="4:12" x14ac:dyDescent="0.35">
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
@@ -919,7 +901,6 @@
     <row r="29" spans="4:12" x14ac:dyDescent="0.35">
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
@@ -930,7 +911,6 @@
     <row r="30" spans="4:12" x14ac:dyDescent="0.35">
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
@@ -940,14 +920,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="C2:C4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="D2:L2"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="C2:C4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
